--- a/stories/arbres/TREE-COL-009.xlsx
+++ b/stories/arbres/TREE-COL-009.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Inès est avec papa, à l'école. Inès a envie de jouer. papa est là, tout près. On va apprendre : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès écoute papa. Inès entend les mots : écouter, si malaise raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Inès va vers les cubes. Les chaussures font toc toc. papa sourit. Ici, c'est les cubes. Ce n'est pas comme les autres endroits. Inès se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On attend son tour. papa dit : je suis là. On reste ensemble.</t>
+          <t>Inès va vers les cubes. Les chaussures font toc toc. papa sourit. Ici, c'est les cubes. Ce n'est pas comme les autres endroits. Inès se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On attend son tour. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1676,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Inès va vers les cubes. Les chaussures font toc toc. papa sourit. Ici, c'est les cubes. Ce n'est pas comme les autres endroits. Inès se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On attend son tour.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1862,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2035,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès respire. Inès retient : écouter, si malaise raconter à la maison. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2183,6 +2226,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2345,6 +2393,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a choisi une pomme. On entend un oiseau. Une pomme reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès répète tout bas : écouter, si malaise raconter à la maison. On se tait une seconde. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2531,6 +2584,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2693,6 +2751,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint le chat. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de les cubes, une pomme et le chat. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2918,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3085,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint le chien. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de les cubes, une pomme et le chien. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3252,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3419,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint la poule. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de les cubes, une pomme et la poule. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3586,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3665,6 +3753,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a choisi un yaourt. Ça sent le pain chaud. Un yaourt reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès répète tout bas : écouter, si malaise raconter à la maison. On se tient la main. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3851,6 +3944,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4013,6 +4111,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint le chat. Une feuille tombe. On attend son tour. Cette fin-là est celle de les cubes, un yaourt et le chat. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4175,6 +4278,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4337,6 +4445,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint le chien. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de les cubes, un yaourt et le chien. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4499,6 +4612,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4661,6 +4779,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint la poule. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de les cubes, un yaourt et la poule. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4823,6 +4946,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4985,6 +5113,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a choisi un morceau de pain. Le vent est doux. Un morceau de pain reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès répète tout bas : écouter, si malaise raconter à la maison. On range un objet. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5171,6 +5304,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5333,6 +5471,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint le chat. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de les cubes, un morceau de pain et le chat. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5495,6 +5638,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5657,6 +5805,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint le chien. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de les cubes, un morceau de pain et le chien. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5819,6 +5972,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5981,6 +6139,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint la poule. La lumière est claire. On rit un peu. Cette fin-là est celle de les cubes, un morceau de pain et la poule. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6143,6 +6306,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6167,7 +6335,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Inès va vers le livre. La couverture est douce. papa sourit. Ici, c'est le livre. Ce n'est pas comme les autres endroits. Inès se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On montre du doigt, sans courir. papa dit : je suis là. On reste ensemble.</t>
+          <t>Inès va vers le livre. La couverture est douce. papa sourit. Ici, c'est le livre. Ce n'est pas comme les autres endroits. Inès se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On montre du doigt, sans courir. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6305,6 +6473,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Inès va vers le livre. La couverture est douce. papa sourit. Ici, c'est le livre. Ce n'est pas comme les autres endroits. Inès se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On montre du doigt, sans courir.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6485,6 +6659,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
         </is>
       </c>
     </row>
@@ -6653,6 +6832,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès respire. Inès retient : écouter, si malaise raconter à la maison. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6839,6 +7023,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7001,6 +7190,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a choisi une pomme. Le sol est un peu froid. Une pomme reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès répète tout bas : écouter, si malaise raconter à la maison. On se tait une seconde. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7187,6 +7381,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7349,6 +7548,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint le chat. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de le livre, une pomme et le chat. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7511,6 +7715,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7673,6 +7882,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint le chien. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de le livre, une pomme et le chien. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7835,6 +8049,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7997,6 +8216,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint la poule. Un vélo passe au loin. On se tait une seconde. Cette fin-là est celle de le livre, une pomme et la poule. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8159,6 +8383,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8321,6 +8550,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a choisi un yaourt. Une feuille tombe. Un yaourt reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès répète tout bas : écouter, si malaise raconter à la maison. On se tient la main. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8507,6 +8741,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8669,6 +8908,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint le chat. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de le livre, un yaourt et le chat. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8831,6 +9075,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8993,6 +9242,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint le chien. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de le livre, un yaourt et le chien. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9155,6 +9409,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9317,6 +9576,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint la poule. La lumière est claire. On se tait une seconde. Cette fin-là est celle de le livre, un yaourt et la poule. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9479,6 +9743,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9641,6 +9910,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a choisi un morceau de pain. L'eau coule, tout petit bruit. Un morceau de pain reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès répète tout bas : écouter, si malaise raconter à la maison. On range un objet. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9827,6 +10101,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9989,6 +10268,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint le chat. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de le livre, un morceau de pain et le chat. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10151,6 +10435,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10313,6 +10602,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint le chien. La lumière est claire. On rit un peu. Cette fin-là est celle de le livre, un morceau de pain et le chien. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10475,6 +10769,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10637,6 +10936,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint la poule. Il y a des miettes sur la table. On se tait une seconde. Cette fin-là est celle de le livre, un morceau de pain et la poule. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10799,6 +11103,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10823,7 +11132,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Inès va vers la dînette. On entend un oiseau. papa sourit. Ici, c'est la dînette. Ce n'est pas comme les autres endroits. Inès se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On rit un peu. papa dit : je suis là. On reste ensemble.</t>
+          <t>Inès va vers la dînette. On entend un oiseau. papa sourit. Ici, c'est la dînette. Ce n'est pas comme les autres endroits. Inès se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On rit un peu. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10961,6 +11270,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Inès va vers la dînette. On entend un oiseau. papa sourit. Ici, c'est la dînette. Ce n'est pas comme les autres endroits. Inès se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On rit un peu.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11141,6 +11456,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
         </is>
       </c>
     </row>
@@ -11309,6 +11629,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès respire. Inès retient : écouter, si malaise raconter à la maison. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11495,6 +11820,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11657,6 +11987,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a choisi une pomme. Un vélo passe au loin. Une pomme reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès répète tout bas : écouter, si malaise raconter à la maison. On se tait une seconde. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11843,6 +12178,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12005,6 +12345,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint le chat. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de la dînette, une pomme et le chat. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12167,6 +12512,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12329,6 +12679,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint le chien. Un vélo passe au loin. On se tait une seconde. Cette fin-là est celle de la dînette, une pomme et le chien. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12491,6 +12846,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12653,6 +13013,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint la poule. La lumière est claire. On se tient la main. Cette fin-là est celle de la dînette, une pomme et la poule. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12815,6 +13180,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12977,6 +13347,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a choisi un yaourt. La lumière est claire. Un yaourt reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès répète tout bas : écouter, si malaise raconter à la maison. On se tient la main. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13163,6 +13538,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13325,6 +13705,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint le chat. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de la dînette, un yaourt et le chat. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13487,6 +13872,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13649,6 +14039,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint le chien. La lumière est claire. On se tait une seconde. Cette fin-là est celle de la dînette, un yaourt et le chien. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13811,6 +14206,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13973,6 +14373,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint la poule. Il y a des miettes sur la table. On se tient la main. Cette fin-là est celle de la dînette, un yaourt et la poule. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14135,6 +14540,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14297,6 +14707,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a choisi un morceau de pain. Il y a des miettes sur la table. Un morceau de pain reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès répète tout bas : écouter, si malaise raconter à la maison. On range un objet. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14483,6 +14898,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14645,6 +15065,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint le chat. La lumière est claire. On rit un peu. Cette fin-là est celle de la dînette, un morceau de pain et le chat. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14807,6 +15232,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14969,6 +15399,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint le chien. Il y a des miettes sur la table. On se tait une seconde. Cette fin-là est celle de la dînette, un morceau de pain et le chien. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15131,6 +15566,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15293,6 +15733,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint la poule. Un chat miaule une fois. On se tient la main. Cette fin-là est celle de la dînette, un morceau de pain et la poule. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15455,6 +15900,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15473,7 +15923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15490,6 +15940,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-COL-009.xlsx
+++ b/stories/arbres/TREE-COL-009.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Inès est avec papa, à l'école. Inès a envie de jouer. papa est là, tout près. On va apprendre : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès écoute papa. Inès entend les mots : écouter, si malaise raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1689,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1869,6 +1877,7 @@
           <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2040,6 +2049,7 @@
           <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès respire. Inès retient : écouter, si malaise raconter à la maison. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2231,6 +2241,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2398,6 +2409,7 @@
           <t>narrateur|Inès a choisi une pomme. On entend un oiseau. Une pomme reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès répète tout bas : écouter, si malaise raconter à la maison. On se tait une seconde. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2587,6 +2599,11 @@
       <c r="AW9" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -2756,6 +2773,7 @@
           <t>narrateur|Inès rejoint le chat. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de les cubes, une pomme et le chat. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2923,6 +2941,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3090,6 +3109,11 @@
           <t>narrateur|Inès rejoint le chien. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de les cubes, une pomme et le chien. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3257,6 +3281,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3424,6 +3449,7 @@
           <t>narrateur|Inès rejoint la poule. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de les cubes, une pomme et la poule. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3591,6 +3617,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3758,6 +3785,7 @@
           <t>narrateur|Inès a choisi un yaourt. Ça sent le pain chaud. Un yaourt reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès répète tout bas : écouter, si malaise raconter à la maison. On se tient la main. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3947,6 +3975,11 @@
       <c r="AW17" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -4116,6 +4149,7 @@
           <t>narrateur|Inès rejoint le chat. Une feuille tombe. On attend son tour. Cette fin-là est celle de les cubes, un yaourt et le chat. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4283,6 +4317,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4450,6 +4485,11 @@
           <t>narrateur|Inès rejoint le chien. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de les cubes, un yaourt et le chien. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4617,6 +4657,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4784,6 +4825,7 @@
           <t>narrateur|Inès rejoint la poule. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de les cubes, un yaourt et la poule. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4951,6 +4993,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5118,6 +5161,7 @@
           <t>narrateur|Inès a choisi un morceau de pain. Le vent est doux. Un morceau de pain reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès répète tout bas : écouter, si malaise raconter à la maison. On range un objet. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5307,6 +5351,11 @@
       <c r="AW25" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -5476,6 +5525,7 @@
           <t>narrateur|Inès rejoint le chat. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de les cubes, un morceau de pain et le chat. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5643,6 +5693,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5810,6 +5861,11 @@
           <t>narrateur|Inès rejoint le chien. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de les cubes, un morceau de pain et le chien. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5977,6 +6033,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6144,6 +6201,7 @@
           <t>narrateur|Inès rejoint la poule. La lumière est claire. On rit un peu. Cette fin-là est celle de les cubes, un morceau de pain et la poule. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6311,6 +6369,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6479,6 +6538,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6666,6 +6726,7 @@
           <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6837,6 +6898,7 @@
           <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès respire. Inès retient : écouter, si malaise raconter à la maison. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7028,6 +7090,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7195,6 +7258,7 @@
           <t>narrateur|Inès a choisi une pomme. Le sol est un peu froid. Une pomme reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès répète tout bas : écouter, si malaise raconter à la maison. On se tait une seconde. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7384,6 +7448,11 @@
       <c r="AW37" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -7553,6 +7622,7 @@
           <t>narrateur|Inès rejoint le chat. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de le livre, une pomme et le chat. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7720,6 +7790,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7887,6 +7958,11 @@
           <t>narrateur|Inès rejoint le chien. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de le livre, une pomme et le chien. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8054,6 +8130,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8221,6 +8298,7 @@
           <t>narrateur|Inès rejoint la poule. Un vélo passe au loin. On se tait une seconde. Cette fin-là est celle de le livre, une pomme et la poule. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8388,6 +8466,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8555,6 +8634,7 @@
           <t>narrateur|Inès a choisi un yaourt. Une feuille tombe. Un yaourt reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès répète tout bas : écouter, si malaise raconter à la maison. On se tient la main. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8744,6 +8824,11 @@
       <c r="AW45" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -8913,6 +8998,7 @@
           <t>narrateur|Inès rejoint le chat. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de le livre, un yaourt et le chat. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9080,6 +9166,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9247,6 +9334,11 @@
           <t>narrateur|Inès rejoint le chien. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de le livre, un yaourt et le chien. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9414,6 +9506,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9581,6 +9674,7 @@
           <t>narrateur|Inès rejoint la poule. La lumière est claire. On se tait une seconde. Cette fin-là est celle de le livre, un yaourt et la poule. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9748,6 +9842,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9915,6 +10010,7 @@
           <t>narrateur|Inès a choisi un morceau de pain. L'eau coule, tout petit bruit. Un morceau de pain reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès répète tout bas : écouter, si malaise raconter à la maison. On range un objet. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10104,6 +10200,11 @@
       <c r="AW53" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -10273,6 +10374,7 @@
           <t>narrateur|Inès rejoint le chat. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de le livre, un morceau de pain et le chat. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10440,6 +10542,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10607,6 +10710,11 @@
           <t>narrateur|Inès rejoint le chien. La lumière est claire. On rit un peu. Cette fin-là est celle de le livre, un morceau de pain et le chien. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10774,6 +10882,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10941,6 +11050,7 @@
           <t>narrateur|Inès rejoint la poule. Il y a des miettes sur la table. On se tait une seconde. Cette fin-là est celle de le livre, un morceau de pain et la poule. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11108,6 +11218,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11276,6 +11387,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11463,6 +11575,7 @@
           <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11634,6 +11747,7 @@
           <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès respire. Inès retient : écouter, si malaise raconter à la maison. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11825,6 +11939,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11992,6 +12107,7 @@
           <t>narrateur|Inès a choisi une pomme. Un vélo passe au loin. Une pomme reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès répète tout bas : écouter, si malaise raconter à la maison. On se tait une seconde. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12181,6 +12297,11 @@
       <c r="AW65" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -12350,6 +12471,7 @@
           <t>narrateur|Inès rejoint le chat. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de la dînette, une pomme et le chat. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12517,6 +12639,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12684,6 +12807,11 @@
           <t>narrateur|Inès rejoint le chien. Un vélo passe au loin. On se tait une seconde. Cette fin-là est celle de la dînette, une pomme et le chien. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12851,6 +12979,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13018,6 +13147,7 @@
           <t>narrateur|Inès rejoint la poule. La lumière est claire. On se tient la main. Cette fin-là est celle de la dînette, une pomme et la poule. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13185,6 +13315,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13352,6 +13483,7 @@
           <t>narrateur|Inès a choisi un yaourt. La lumière est claire. Un yaourt reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès répète tout bas : écouter, si malaise raconter à la maison. On se tient la main. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13541,6 +13673,11 @@
       <c r="AW73" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -13710,6 +13847,7 @@
           <t>narrateur|Inès rejoint le chat. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de la dînette, un yaourt et le chat. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13877,6 +14015,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14044,6 +14183,11 @@
           <t>narrateur|Inès rejoint le chien. La lumière est claire. On se tait une seconde. Cette fin-là est celle de la dînette, un yaourt et le chien. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14211,6 +14355,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14378,6 +14523,7 @@
           <t>narrateur|Inès rejoint la poule. Il y a des miettes sur la table. On se tient la main. Cette fin-là est celle de la dînette, un yaourt et la poule. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14545,6 +14691,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14712,6 +14859,7 @@
           <t>narrateur|Inès a choisi un morceau de pain. Il y a des miettes sur la table. Un morceau de pain reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès répète tout bas : écouter, si malaise raconter à la maison. On range un objet. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14901,6 +15049,11 @@
       <c r="AW81" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -15070,6 +15223,7 @@
           <t>narrateur|Inès rejoint le chat. La lumière est claire. On rit un peu. Cette fin-là est celle de la dînette, un morceau de pain et le chat. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15237,6 +15391,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15404,6 +15559,11 @@
           <t>narrateur|Inès rejoint le chien. Il y a des miettes sur la table. On se tait une seconde. Cette fin-là est celle de la dînette, un morceau de pain et le chien. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15571,6 +15731,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15738,6 +15899,7 @@
           <t>narrateur|Inès rejoint la poule. Un chat miaule une fois. On se tient la main. Cette fin-là est celle de la dînette, un morceau de pain et la poule. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15905,6 +16067,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15923,7 +16086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15947,6 +16110,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15961,7 +16138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16148,6 +16325,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-COL-009.xlsx
+++ b/stories/arbres/TREE-COL-009.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Écouter la maîtresse, en parler à la maison — à l'école</t>
+          <t>Le bouton rouge de Nina</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le radiateur tic. Nina accroche son manteau. Elle écoute la maîtresse. Un chuchotement serre son ventre. Elle raconte à papa et maman, puis elle joue.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aujourd'hui, Inès est avec papa, à l'école. Inès a envie de jouer. papa est là, tout près. On va apprendre : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès écoute papa. Inès entend les mots : écouter, si malaise raconter à la maison.</t>
+          <t>Le radiateur de la classe fait tic, tout chaud. Un bouton rouge attend sur le crochet. La vitre est embuée, toute douce. Papa trace un petit rond du doigt. Ça sent la cire des crayons. Ça sent aussi le savon des mains. Le sol brille encore, après la serpillière. Le cartable de Nina pose contre le casier. Un crayon bleu dépasse, tout lisse. Tu as vu le bouton rouge ? Il est tout seul. On le range dans la poche. Tu écoutes la maîtresse, d'accord ? D'accord, maman. Et si tu as un malaise ? Tu racontes à papa ou maman. Je raconte à la maison. En ce moment, Nina accroche son manteau. Le manteau est encore un peu froid. La classe est calme, un peu claire. La maîtresse parle près du tableau. Nina écoute, tout près. Les mots arrivent, tout doux. Un camarade se penche près de l'oreille. Il parle tout bas. Nina sent un malaise. Son ventre se serre, tout petit. Papa. J'ai un malaise. Tu as bien fait de le dire. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, papa. Les cubes attendent sur le tapis. Le livre est près de la fenêtre. La dînette brille, toute petite. Tu es prête ? Oui, maman.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,7 +1337,45 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Aujourd'hui, Inès est avec papa, à l'école. Inès a envie de jouer. papa est là, tout près. On va apprendre : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès écoute papa. Inès entend les mots : écouter, si malaise raconter à la maison.</t>
+          <t>narrateur|Le radiateur de la classe fait tic, tout chaud.
+narrateur|Un bouton rouge attend sur le crochet.
+narrateur|La vitre est embuée, toute douce.
+narrateur|Papa trace un petit rond du doigt.
+narrateur|Ça sent la cire des crayons.
+narrateur|Ça sent aussi le savon des mains.
+narrateur|Le sol brille encore, après la serpillière.
+narrateur|Le cartable de Nina pose contre le casier.
+narrateur|Un crayon bleu dépasse, tout lisse.
+maman|Tu as vu le bouton rouge ?
+enfant-f|Il est tout seul.
+papa|On le range dans la poche.
+maman|Tu écoutes la maîtresse, d'accord ?
+enfant-f|D'accord, maman.
+papa|Et si tu as un malaise ?
+papa|Tu racontes à papa ou maman.
+enfant-f|Je raconte à la maison.
+narrateur|En ce moment, Nina accroche son manteau.
+narrateur|Le manteau est encore un peu froid.
+narrateur|La classe est calme, un peu claire.
+narrateur|La maîtresse parle près du tableau.
+narrateur|Nina écoute, tout près.
+narrateur|Les mots arrivent, tout doux.
+narrateur|Un camarade se penche près de l'oreille.
+narrateur|Il parle tout bas.
+narrateur|Nina sent un malaise.
+narrateur|Son ventre se serre, tout petit.
+enfant-f|Papa. J'ai un malaise.
+papa|Tu as bien fait de le dire.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, papa.
+narrateur|Les cubes attendent sur le tapis.
+narrateur|Le livre est près de la fenêtre.
+narrateur|La dînette brille, toute petite.
+maman|Tu es prête ?
+enfant-f|Oui, maman.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1353,7 +1403,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>Nina va vers quel jeu ? Les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1517,7 +1567,8 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>narrateur|Nina va vers quel jeu ?
+papa|Les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1545,7 +1596,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Inès va vers les cubes. Les chaussures font toc toc. papa sourit. Ici, c'est les cubes. Ce n'est pas comme les autres endroits. Inès se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On attend son tour. Je suis là. On reste ensemble.</t>
+          <t>Nina s'assoit près des cubes. Ils sont en bois, un peu rudes. Un cube rouge fait toc, sur le tapis. Papa s'assoit aussi, tout près. Tu écoutes encore, Nina ? J'écoute la maîtresse. Et le malaise ? Je raconte à la maison. Oui. À papa ou à maman. La maîtresse parle, plus loin. Nina écoute, les mains sur un cube. Bravo. Tu as écouté. Tu as raconté aussi. Mon ventre est plus calme. Le cube rouge reste dans sa main.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1685,8 +1736,21 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Inès va vers les cubes. Les chaussures font toc toc. papa sourit. Ici, c'est les cubes. Ce n'est pas comme les autres endroits. Inès se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On attend son tour.
-papa|Je suis là. On reste ensemble.</t>
+          <t>narrateur|Nina s'assoit près des cubes.
+narrateur|Ils sont en bois, un peu rudes.
+narrateur|Un cube rouge fait toc, sur le tapis.
+narrateur|Papa s'assoit aussi, tout près.
+maman|Tu écoutes encore, Nina ?
+enfant-f|J'écoute la maîtresse.
+papa|Et le malaise ?
+enfant-f|Je raconte à la maison.
+maman|Oui. À papa ou à maman.
+narrateur|La maîtresse parle, plus loin.
+narrateur|Nina écoute, les mains sur un cube.
+papa|Bravo. Tu as écouté.
+maman|Tu as raconté aussi.
+enfant-f|Mon ventre est plus calme.
+narrateur|Le cube rouge reste dans sa main.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1714,7 +1778,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
+          <t>Nina a un malaise. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1874,7 +1938,8 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
+          <t>narrateur|Nina a un malaise.
+narrateur|Que fait-elle ?</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1902,7 +1967,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès respire. Inès retient : écouter, si malaise raconter à la maison. On continue, avec papa.</t>
+          <t>Oui. Elle raconte à papa ou maman. On écoute la maîtresse. Nina respire, tout calme. Bravo, Nina. Tu as fait du bon travail. Merci, papa. On continue, tout doux.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2046,7 +2111,14 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès respire. Inès retient : écouter, si malaise raconter à la maison. On continue, avec papa.</t>
+          <t>narrateur|Oui.
+papa|Elle raconte à papa ou maman.
+maman|On écoute la maîtresse.
+narrateur|Nina respire, tout calme.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+enfant-f|Merci, papa.
+maman|On continue, tout doux.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2074,7 +2146,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+          <t>On prend quel goûter ? Une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2238,7 +2310,8 @@
       <c r="AV7" s="2" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+          <t>narrateur|On prend quel goûter ?
+maman|Une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr"/>
@@ -2266,7 +2339,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Inès a choisi une pomme. On entend un oiseau. Une pomme reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès répète tout bas : écouter, si malaise raconter à la maison. On se tait une seconde. maman n'est pas loin.</t>
+          <t>Nina a choisi une pomme, près des cubes. La pomme est rouge, un peu froide. Un oiseau chante derrière la vitre. Tu as encore le malaise ? Un peu. Je raconte. On écoute la maîtresse. Puis on raconte à la maison. Bravo. Tu as dit les mots. J'écoute. Je raconte. La pomme brille dans sa main. Le ventre se desserre, tout doux. On reste ensemble. Une feuille colle encore à la vitre.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2406,7 +2479,19 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Inès a choisi une pomme. On entend un oiseau. Une pomme reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès répète tout bas : écouter, si malaise raconter à la maison. On se tait une seconde. maman n'est pas loin.</t>
+          <t>narrateur|Nina a choisi une pomme, près des cubes.
+narrateur|La pomme est rouge, un peu froide.
+narrateur|Un oiseau chante derrière la vitre.
+papa|Tu as encore le malaise ?
+enfant-f|Un peu. Je raconte.
+maman|On écoute la maîtresse.
+maman|Puis on raconte à la maison.
+papa|Bravo. Tu as dit les mots.
+enfant-f|J'écoute. Je raconte.
+narrateur|La pomme brille dans sa main.
+maman|Le ventre se desserre, tout doux.
+papa|On reste ensemble.
+narrateur|Une feuille colle encore à la vitre.</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr"/>
@@ -2434,7 +2519,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le chat, le chien, ou la poule.</t>
+          <t>On va voir qui, dans la cour ? Le chat, le chien, ou la poule.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2598,7 +2683,8 @@
       <c r="AV9" s="2" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+          <t>narrateur|On va voir qui, dans la cour ?
+papa|Le chat, le chien, ou la poule.</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -2630,7 +2716,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint le chat. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de les cubes, une pomme et le chat. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>Le chat se frotte aux cubes, tout doux. Une pomme roule, tout près du tapis. Nina rejoint le chat. La cour sent l'herbe et la terre. J'ai écouté la maîtresse. J'ai eu un malaise. Je raconte à la maison. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à papa ou maman. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement. Elle se souvient des cubes, et d'une pomme.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2770,7 +2856,22 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Inès rejoint le chat. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de les cubes, une pomme et le chat. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>narrateur|Le chat se frotte aux cubes, tout doux.
+narrateur|Une pomme roule, tout près du tapis.
+narrateur|Nina rejoint le chat.
+narrateur|La cour sent l'herbe et la terre.
+enfant-f|J'ai écouté la maîtresse.
+enfant-f|J'ai eu un malaise.
+enfant-f|Je raconte à la maison.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à papa ou maman.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+narrateur|Elle se souvient des cubes, et d'une pomme.</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr"/>
@@ -2798,7 +2899,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué avec les cubes. Elle a pris une pomme. Elle a vu le chat. Le cube rouge a gardé un poil de chat. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2938,7 +3039,15 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué avec les cubes.
+narrateur|Elle a pris une pomme.
+narrateur|Elle a vu le chat.
+narrateur|Le cube rouge a gardé un poil de chat.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr"/>
@@ -2966,7 +3075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint le chien. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de les cubes, une pomme et le chien. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>Le chien pose le museau près de la pomme. Un cube rouge tremble, tout petit. Nina rejoint le chien. La cour sent l'herbe et la terre. J'ai écouté la maîtresse. J'ai eu un malaise. Je raconte à la maison. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à papa ou maman. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement. Elle se souvient des cubes, et d'une pomme.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3106,7 +3215,22 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Inès rejoint le chien. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de les cubes, une pomme et le chien. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>narrateur|Le chien pose le museau près de la pomme.
+narrateur|Un cube rouge tremble, tout petit.
+narrateur|Nina rejoint le chien.
+narrateur|La cour sent l'herbe et la terre.
+enfant-f|J'ai écouté la maîtresse.
+enfant-f|J'ai eu un malaise.
+enfant-f|Je raconte à la maison.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à papa ou maman.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+narrateur|Elle se souvient des cubes, et d'une pomme.</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -3138,7 +3262,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué avec les cubes. Elle a pris une pomme. Elle a vu le chien. La pomme a une petite marque de museau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3278,7 +3402,15 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué avec les cubes.
+narrateur|Elle a pris une pomme.
+narrateur|Elle a vu le chien.
+narrateur|La pomme a une petite marque de museau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr"/>
@@ -3306,7 +3438,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint la poule. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de les cubes, une pomme et la poule. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>La poule picore à côté d'un cube rouge. La pomme attend dans la main de Nina. Nina rejoint la poule. La cour sent l'herbe et la terre. J'ai écouté la maîtresse. J'ai eu un malaise. Je raconte à la maison. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à papa ou maman. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement. Elle se souvient des cubes, et d'une pomme.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3446,7 +3578,22 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Inès rejoint la poule. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de les cubes, une pomme et la poule. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>narrateur|La poule picore à côté d'un cube rouge.
+narrateur|La pomme attend dans la main de Nina.
+narrateur|Nina rejoint la poule.
+narrateur|La cour sent l'herbe et la terre.
+enfant-f|J'ai écouté la maîtresse.
+enfant-f|J'ai eu un malaise.
+enfant-f|Je raconte à la maison.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à papa ou maman.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+narrateur|Elle se souvient des cubes, et d'une pomme.</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr"/>
@@ -3474,7 +3621,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué avec les cubes. Elle a pris une pomme. Elle a vu la poule. Un cube rouge a une plume, tout léger. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3614,7 +3761,15 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué avec les cubes.
+narrateur|Elle a pris une pomme.
+narrateur|Elle a vu la poule.
+narrateur|Un cube rouge a une plume, tout léger.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr"/>
@@ -3642,7 +3797,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Inès a choisi un yaourt. Ça sent le pain chaud. Un yaourt reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès répète tout bas : écouter, si malaise raconter à la maison. On se tient la main. maman n'est pas loin.</t>
+          <t>Nina a choisi un yaourt, près des cubes. Le pot est frais, tout lisse. Ça sent le lait, tout doux. Tu écoutes encore ? J'écoute la maîtresse. Et le malaise ? Je raconte à papa ou maman. Oui. À la maison aussi. Bravo, Nina. La cuillère fait un petit clic. Tu as fait du bon travail. Merci. Le pot reste près des cubes.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3782,7 +3937,19 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Inès a choisi un yaourt. Ça sent le pain chaud. Un yaourt reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès répète tout bas : écouter, si malaise raconter à la maison. On se tient la main. maman n'est pas loin.</t>
+          <t>narrateur|Nina a choisi un yaourt, près des cubes.
+narrateur|Le pot est frais, tout lisse.
+narrateur|Ça sent le lait, tout doux.
+maman|Tu écoutes encore ?
+enfant-f|J'écoute la maîtresse.
+papa|Et le malaise ?
+enfant-f|Je raconte à papa ou maman.
+maman|Oui. À la maison aussi.
+papa|Bravo, Nina.
+narrateur|La cuillère fait un petit clic.
+maman|Tu as fait du bon travail.
+enfant-f|Merci.
+narrateur|Le pot reste près des cubes.</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr"/>
@@ -3810,7 +3977,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le chat, le chien, ou la poule.</t>
+          <t>On va voir qui, dans la cour ? Le chat, le chien, ou la poule.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3974,7 +4141,8 @@
       <c r="AV17" s="2" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+          <t>narrateur|On va voir qui, dans la cour ?
+papa|Le chat, le chien, ou la poule.</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -4006,7 +4174,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint le chat. Une feuille tombe. On attend son tour. Cette fin-là est celle de les cubes, un yaourt et le chat. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>Le chat regarde le pot de yaourt, tout calme. Un cube bleu reste contre sa patte. Nina rejoint le chat. La cour sent l'herbe et la terre. J'ai écouté la maîtresse. J'ai eu un malaise. Je raconte à la maison. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à papa ou maman. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement. Elle se souvient des cubes, et d'un yaourt.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4146,7 +4314,22 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Inès rejoint le chat. Une feuille tombe. On attend son tour. Cette fin-là est celle de les cubes, un yaourt et le chat. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>narrateur|Le chat regarde le pot de yaourt, tout calme.
+narrateur|Un cube bleu reste contre sa patte.
+narrateur|Nina rejoint le chat.
+narrateur|La cour sent l'herbe et la terre.
+enfant-f|J'ai écouté la maîtresse.
+enfant-f|J'ai eu un malaise.
+enfant-f|Je raconte à la maison.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à papa ou maman.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+narrateur|Elle se souvient des cubes, et d'un yaourt.</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr"/>
@@ -4174,7 +4357,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué avec les cubes. Elle a pris un yaourt. Elle a vu le chat. Le pot de yaourt est vide, tout propre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4314,7 +4497,15 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué avec les cubes.
+narrateur|Elle a pris un yaourt.
+narrateur|Elle a vu le chat.
+narrateur|Le pot de yaourt est vide, tout propre.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr"/>
@@ -4342,7 +4533,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint le chien. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de les cubes, un yaourt et le chien. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>Le chien attend près du pot, la queue douce. Les cubes font un petit tas. Nina rejoint le chien. La cour sent l'herbe et la terre. J'ai écouté la maîtresse. J'ai eu un malaise. Je raconte à la maison. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à papa ou maman. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement. Elle se souvient des cubes, et d'un yaourt.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4482,7 +4673,22 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Inès rejoint le chien. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de les cubes, un yaourt et le chien. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>narrateur|Le chien attend près du pot, la queue douce.
+narrateur|Les cubes font un petit tas.
+narrateur|Nina rejoint le chien.
+narrateur|La cour sent l'herbe et la terre.
+enfant-f|J'ai écouté la maîtresse.
+enfant-f|J'ai eu un malaise.
+enfant-f|Je raconte à la maison.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à papa ou maman.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+narrateur|Elle se souvient des cubes, et d'un yaourt.</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
@@ -4514,7 +4720,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué avec les cubes. Elle a pris un yaourt. Elle a vu le chien. La queue du chien a bougé un cube. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4654,7 +4860,15 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué avec les cubes.
+narrateur|Elle a pris un yaourt.
+narrateur|Elle a vu le chien.
+narrateur|La queue du chien a bougé un cube.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr"/>
@@ -4682,7 +4896,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint la poule. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de les cubes, un yaourt et la poule. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>La poule fait un petit cot près des cubes. Le yaourt reste au frais, sur la table. Nina rejoint la poule. La cour sent l'herbe et la terre. J'ai écouté la maîtresse. J'ai eu un malaise. Je raconte à la maison. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à papa ou maman. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement. Elle se souvient des cubes, et d'un yaourt.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4822,7 +5036,22 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Inès rejoint la poule. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de les cubes, un yaourt et la poule. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>narrateur|La poule fait un petit cot près des cubes.
+narrateur|Le yaourt reste au frais, sur la table.
+narrateur|Nina rejoint la poule.
+narrateur|La cour sent l'herbe et la terre.
+enfant-f|J'ai écouté la maîtresse.
+enfant-f|J'ai eu un malaise.
+enfant-f|Je raconte à la maison.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à papa ou maman.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+narrateur|Elle se souvient des cubes, et d'un yaourt.</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr"/>
@@ -4850,7 +5079,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué avec les cubes. Elle a pris un yaourt. Elle a vu la poule. Un cot cot reste dans la classe, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4990,7 +5219,15 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué avec les cubes.
+narrateur|Elle a pris un yaourt.
+narrateur|Elle a vu la poule.
+narrateur|Un cot cot reste dans la classe, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr"/>
@@ -5018,7 +5255,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Inès a choisi un morceau de pain. Le vent est doux. Un morceau de pain reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès répète tout bas : écouter, si malaise raconter à la maison. On range un objet. maman n'est pas loin.</t>
+          <t>Nina a choisi un morceau de pain, près des cubes. La croûte est un peu chaude. Des miettes tombent sur la table. On écoute, même avec le pain ? J'écoute la maîtresse. Si malaise, tu racontes. À la maison. À papa ou à maman. Bravo. C'est ça. Nina souffle une miette, tout léger. Tu as écouté. Tu as raconté. Mon ventre est calme. Le pain reste à sa place.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5158,7 +5395,19 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Inès a choisi un morceau de pain. Le vent est doux. Un morceau de pain reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès répète tout bas : écouter, si malaise raconter à la maison. On range un objet. maman n'est pas loin.</t>
+          <t>narrateur|Nina a choisi un morceau de pain, près des cubes.
+narrateur|La croûte est un peu chaude.
+narrateur|Des miettes tombent sur la table.
+papa|On écoute, même avec le pain ?
+enfant-f|J'écoute la maîtresse.
+maman|Si malaise, tu racontes.
+enfant-f|À la maison.
+papa|À papa ou à maman.
+maman|Bravo. C'est ça.
+narrateur|Nina souffle une miette, tout léger.
+papa|Tu as écouté. Tu as raconté.
+enfant-f|Mon ventre est calme.
+narrateur|Le pain reste à sa place.</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr"/>
@@ -5186,7 +5435,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le chat, le chien, ou la poule.</t>
+          <t>On va voir qui, dans la cour ? Le chat, le chien, ou la poule.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5350,7 +5599,8 @@
       <c r="AV25" s="2" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+          <t>narrateur|On va voir qui, dans la cour ?
+papa|Le chat, le chien, ou la poule.</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
@@ -5382,7 +5632,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint le chat. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de les cubes, un morceau de pain et le chat. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>Le chat marche entre les miettes, tout léger. Un cube jaune garde une miette. Nina rejoint le chat. La cour sent l'herbe et la terre. J'ai écouté la maîtresse. J'ai eu un malaise. Je raconte à la maison. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à papa ou maman. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement. Elle se souvient des cubes, et d'un morceau de pain.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5522,7 +5772,22 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Inès rejoint le chat. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de les cubes, un morceau de pain et le chat. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>narrateur|Le chat marche entre les miettes, tout léger.
+narrateur|Un cube jaune garde une miette.
+narrateur|Nina rejoint le chat.
+narrateur|La cour sent l'herbe et la terre.
+enfant-f|J'ai écouté la maîtresse.
+enfant-f|J'ai eu un malaise.
+enfant-f|Je raconte à la maison.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à papa ou maman.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+narrateur|Elle se souvient des cubes, et d'un morceau de pain.</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr"/>
@@ -5550,7 +5815,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué avec les cubes. Elle a pris un morceau de pain. Elle a vu le chat. Une miette dort encore sur le tapis. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5690,7 +5955,15 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué avec les cubes.
+narrateur|Elle a pris un morceau de pain.
+narrateur|Elle a vu le chat.
+narrateur|Une miette dort encore sur le tapis.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr"/>
@@ -5718,7 +5991,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint le chien. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de les cubes, un morceau de pain et le chien. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>Le chien sent le pain, sans se presser. Les cubes restent en rang, tout sages. Nina rejoint le chien. La cour sent l'herbe et la terre. J'ai écouté la maîtresse. J'ai eu un malaise. Je raconte à la maison. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à papa ou maman. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement. Elle se souvient des cubes, et d'un morceau de pain.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5858,7 +6131,22 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Inès rejoint le chien. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de les cubes, un morceau de pain et le chien. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>narrateur|Le chien sent le pain, sans se presser.
+narrateur|Les cubes restent en rang, tout sages.
+narrateur|Nina rejoint le chien.
+narrateur|La cour sent l'herbe et la terre.
+enfant-f|J'ai écouté la maîtresse.
+enfant-f|J'ai eu un malaise.
+enfant-f|Je raconte à la maison.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à papa ou maman.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+narrateur|Elle se souvient des cubes, et d'un morceau de pain.</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
@@ -5890,7 +6178,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué avec les cubes. Elle a pris un morceau de pain. Elle a vu le chien. Le pain a tiédi près du radiateur. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6030,7 +6318,15 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué avec les cubes.
+narrateur|Elle a pris un morceau de pain.
+narrateur|Elle a vu le chien.
+narrateur|Le pain a tiédi près du radiateur.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr"/>
@@ -6058,7 +6354,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint la poule. La lumière est claire. On rit un peu. Cette fin-là est celle de les cubes, un morceau de pain et la poule. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>La poule picore une miette, près d'un cube. Le pain sent encore le four. Nina rejoint la poule. La cour sent l'herbe et la terre. J'ai écouté la maîtresse. J'ai eu un malaise. Je raconte à la maison. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à papa ou maman. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement. Elle se souvient des cubes, et d'un morceau de pain.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6198,7 +6494,22 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Inès rejoint la poule. La lumière est claire. On rit un peu. Cette fin-là est celle de les cubes, un morceau de pain et la poule. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>narrateur|La poule picore une miette, près d'un cube.
+narrateur|Le pain sent encore le four.
+narrateur|Nina rejoint la poule.
+narrateur|La cour sent l'herbe et la terre.
+enfant-f|J'ai écouté la maîtresse.
+enfant-f|J'ai eu un malaise.
+enfant-f|Je raconte à la maison.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à papa ou maman.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+narrateur|Elle se souvient des cubes, et d'un morceau de pain.</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr"/>
@@ -6226,7 +6537,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué avec les cubes. Elle a pris un morceau de pain. Elle a vu la poule. La poule a laissé une plume sur un cube. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6366,7 +6677,15 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué avec les cubes.
+narrateur|Elle a pris un morceau de pain.
+narrateur|Elle a vu la poule.
+narrateur|La poule a laissé une plume sur un cube.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr"/>
@@ -6394,7 +6713,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Inès va vers le livre. La couverture est douce. papa sourit. Ici, c'est le livre. Ce n'est pas comme les autres endroits. Inès se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On montre du doigt, sans courir. Je suis là. On reste ensemble.</t>
+          <t>Nina ouvre le livre, tout doux. La couverture est un peu rêche. Une page chuchote sous le doigt. Maman s'assoit près de la fenêtre. Tu écoutes l'histoire ? J'écoute la maîtresse aussi. Et si le ventre se serre ? Je raconte à la maison. Oui. Papa ou maman t'écoute. La maîtresse lit, plus loin. Nina écoute, le livre sur les genoux. Bravo, Nina. Tu as écouté. Tu as raconté. Le malaise s'en va, tout doux. Un oiseau passe derrière la vitre.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6534,8 +6853,21 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|Inès va vers le livre. La couverture est douce. papa sourit. Ici, c'est le livre. Ce n'est pas comme les autres endroits. Inès se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On montre du doigt, sans courir.
-papa|Je suis là. On reste ensemble.</t>
+          <t>narrateur|Nina ouvre le livre, tout doux.
+narrateur|La couverture est un peu rêche.
+narrateur|Une page chuchote sous le doigt.
+narrateur|Maman s'assoit près de la fenêtre.
+papa|Tu écoutes l'histoire ?
+enfant-f|J'écoute la maîtresse aussi.
+maman|Et si le ventre se serre ?
+enfant-f|Je raconte à la maison.
+papa|Oui. Papa ou maman t'écoute.
+narrateur|La maîtresse lit, plus loin.
+narrateur|Nina écoute, le livre sur les genoux.
+maman|Bravo, Nina.
+papa|Tu as écouté. Tu as raconté.
+enfant-f|Le malaise s'en va, tout doux.
+narrateur|Un oiseau passe derrière la vitre.</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr"/>
@@ -6563,7 +6895,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
+          <t>Nina raconte à qui ?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -6723,7 +7055,7 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
+          <t>narrateur|Nina raconte à qui ?</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr"/>
@@ -6751,7 +7083,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès respire. Inès retient : écouter, si malaise raconter à la maison. On continue, avec papa.</t>
+          <t>Oui. À papa. À maman. À la maison. On écoute la maîtresse aussi. Nina tient encore le livre. Bravo. Tu as raconté le malaise. Je raconte. C'est ça.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6895,7 +7227,14 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès respire. Inès retient : écouter, si malaise raconter à la maison. On continue, avec papa.</t>
+          <t>narrateur|Oui.
+maman|À papa. À maman. À la maison.
+papa|On écoute la maîtresse aussi.
+narrateur|Nina tient encore le livre.
+maman|Bravo.
+maman|Tu as raconté le malaise.
+enfant-f|Je raconte.
+papa|C'est ça.</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr"/>
@@ -6923,7 +7262,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+          <t>On prend quel goûter ? Une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7087,7 +7426,8 @@
       <c r="AV35" s="2" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+          <t>narrateur|On prend quel goûter ?
+maman|Une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr"/>
@@ -7115,7 +7455,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Inès a choisi une pomme. Le sol est un peu froid. Une pomme reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès répète tout bas : écouter, si malaise raconter à la maison. On se tait une seconde. maman n'est pas loin.</t>
+          <t>Nina a choisi une pomme, près du livre. La pomme est rouge, un peu froide. Un oiseau chante derrière la vitre. Tu as encore le malaise ? Un peu. Je raconte. On écoute la maîtresse. Puis on raconte à la maison. Bravo. Tu as dit les mots. J'écoute. Je raconte. La pomme brille dans sa main. Le ventre se desserre, tout doux. On reste ensemble. Une feuille colle encore à la vitre.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7255,7 +7595,19 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Inès a choisi une pomme. Le sol est un peu froid. Une pomme reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès répète tout bas : écouter, si malaise raconter à la maison. On se tait une seconde. maman n'est pas loin.</t>
+          <t>narrateur|Nina a choisi une pomme, près du livre.
+narrateur|La pomme est rouge, un peu froide.
+narrateur|Un oiseau chante derrière la vitre.
+papa|Tu as encore le malaise ?
+enfant-f|Un peu. Je raconte.
+maman|On écoute la maîtresse.
+maman|Puis on raconte à la maison.
+papa|Bravo. Tu as dit les mots.
+enfant-f|J'écoute. Je raconte.
+narrateur|La pomme brille dans sa main.
+maman|Le ventre se desserre, tout doux.
+papa|On reste ensemble.
+narrateur|Une feuille colle encore à la vitre.</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr"/>
@@ -7283,7 +7635,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le chat, le chien, ou la poule.</t>
+          <t>On va voir qui, dans la cour ? Le chat, le chien, ou la poule.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7447,7 +7799,8 @@
       <c r="AV37" s="2" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+          <t>narrateur|On va voir qui, dans la cour ?
+papa|Le chat, le chien, ou la poule.</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
@@ -7479,7 +7832,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint le chat. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de le livre, une pomme et le chat. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>Le chat s'assoit sur le livre fermé. La pomme brille près de la couverture. Nina rejoint le chat. La cour sent l'herbe et la terre. J'ai écouté la maîtresse. J'ai eu un malaise. Je raconte à la maison. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à papa ou maman. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement. Elle se souvient du livre, et d'une pomme.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7619,7 +7972,22 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Inès rejoint le chat. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de le livre, une pomme et le chat. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>narrateur|Le chat s'assoit sur le livre fermé.
+narrateur|La pomme brille près de la couverture.
+narrateur|Nina rejoint le chat.
+narrateur|La cour sent l'herbe et la terre.
+enfant-f|J'ai écouté la maîtresse.
+enfant-f|J'ai eu un malaise.
+enfant-f|Je raconte à la maison.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à papa ou maman.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+narrateur|Elle se souvient du livre, et d'une pomme.</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr"/>
@@ -7647,7 +8015,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué avec le livre. Elle a pris une pomme. Elle a vu le chat. Le livre a un rond de soleil, tout chaud. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7787,7 +8155,15 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué avec le livre.
+narrateur|Elle a pris une pomme.
+narrateur|Elle a vu le chat.
+narrateur|Le livre a un rond de soleil, tout chaud.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr"/>
@@ -7815,7 +8191,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint le chien. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de le livre, une pomme et le chien. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>Le chien pose la tête près du livre. La pomme roule vers la page. Nina rejoint le chien. La cour sent l'herbe et la terre. J'ai écouté la maîtresse. J'ai eu un malaise. Je raconte à la maison. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à papa ou maman. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement. Elle se souvient du livre, et d'une pomme.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7955,7 +8331,22 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Inès rejoint le chien. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de le livre, une pomme et le chien. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>narrateur|Le chien pose la tête près du livre.
+narrateur|La pomme roule vers la page.
+narrateur|Nina rejoint le chien.
+narrateur|La cour sent l'herbe et la terre.
+enfant-f|J'ai écouté la maîtresse.
+enfant-f|J'ai eu un malaise.
+enfant-f|Je raconte à la maison.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à papa ou maman.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+narrateur|Elle se souvient du livre, et d'une pomme.</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
@@ -7987,7 +8378,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué avec le livre. Elle a pris une pomme. Elle a vu le chien. La page a gardé une odeur de pomme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8127,7 +8518,15 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué avec le livre.
+narrateur|Elle a pris une pomme.
+narrateur|Elle a vu le chien.
+narrateur|La page a gardé une odeur de pomme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr"/>
@@ -8155,7 +8554,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint la poule. Un vélo passe au loin. On se tait une seconde. Cette fin-là est celle de le livre, une pomme et la poule. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>La poule regarde l'image du livre, de loin. Nina tient encore sa pomme. Nina rejoint la poule. La cour sent l'herbe et la terre. J'ai écouté la maîtresse. J'ai eu un malaise. Je raconte à la maison. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à papa ou maman. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement. Elle se souvient du livre, et d'une pomme.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8295,7 +8694,22 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Inès rejoint la poule. Un vélo passe au loin. On se tait une seconde. Cette fin-là est celle de le livre, une pomme et la poule. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>narrateur|La poule regarde l'image du livre, de loin.
+narrateur|Nina tient encore sa pomme.
+narrateur|Nina rejoint la poule.
+narrateur|La cour sent l'herbe et la terre.
+enfant-f|J'ai écouté la maîtresse.
+enfant-f|J'ai eu un malaise.
+enfant-f|Je raconte à la maison.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à papa ou maman.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+narrateur|Elle se souvient du livre, et d'une pomme.</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr"/>
@@ -8323,7 +8737,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué avec le livre. Elle a pris une pomme. Elle a vu la poule. L'image du livre reste ouverte, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8463,7 +8877,15 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué avec le livre.
+narrateur|Elle a pris une pomme.
+narrateur|Elle a vu la poule.
+narrateur|L'image du livre reste ouverte, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr"/>
@@ -8491,7 +8913,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Inès a choisi un yaourt. Une feuille tombe. Un yaourt reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès répète tout bas : écouter, si malaise raconter à la maison. On se tient la main. maman n'est pas loin.</t>
+          <t>Nina a choisi un yaourt, près du livre. Le pot est frais, tout lisse. Ça sent le lait, tout doux. Tu écoutes encore ? J'écoute la maîtresse. Et le malaise ? Je raconte à papa ou maman. Oui. À la maison aussi. Bravo, Nina. La cuillère fait un petit clic. Tu as fait du bon travail. Merci. Le pot reste près du livre.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8631,7 +9053,19 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Inès a choisi un yaourt. Une feuille tombe. Un yaourt reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès répète tout bas : écouter, si malaise raconter à la maison. On se tient la main. maman n'est pas loin.</t>
+          <t>narrateur|Nina a choisi un yaourt, près du livre.
+narrateur|Le pot est frais, tout lisse.
+narrateur|Ça sent le lait, tout doux.
+maman|Tu écoutes encore ?
+enfant-f|J'écoute la maîtresse.
+papa|Et le malaise ?
+enfant-f|Je raconte à papa ou maman.
+maman|Oui. À la maison aussi.
+papa|Bravo, Nina.
+narrateur|La cuillère fait un petit clic.
+maman|Tu as fait du bon travail.
+enfant-f|Merci.
+narrateur|Le pot reste près du livre.</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr"/>
@@ -8659,7 +9093,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le chat, le chien, ou la poule.</t>
+          <t>On va voir qui, dans la cour ? Le chat, le chien, ou la poule.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8823,7 +9257,8 @@
       <c r="AV45" s="2" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+          <t>narrateur|On va voir qui, dans la cour ?
+papa|Le chat, le chien, ou la poule.</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
@@ -8855,7 +9290,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint le chat. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de le livre, un yaourt et le chat. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>Le chat ronronne contre le livre ouvert. Le pot de yaourt est tout froid. Nina rejoint le chat. La cour sent l'herbe et la terre. J'ai écouté la maîtresse. J'ai eu un malaise. Je raconte à la maison. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à papa ou maman. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement. Elle se souvient du livre, et d'un yaourt.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8995,7 +9430,22 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Inès rejoint le chat. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de le livre, un yaourt et le chat. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>narrateur|Le chat ronronne contre le livre ouvert.
+narrateur|Le pot de yaourt est tout froid.
+narrateur|Nina rejoint le chat.
+narrateur|La cour sent l'herbe et la terre.
+enfant-f|J'ai écouté la maîtresse.
+enfant-f|J'ai eu un malaise.
+enfant-f|Je raconte à la maison.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à papa ou maman.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+narrateur|Elle se souvient du livre, et d'un yaourt.</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr"/>
@@ -9023,7 +9473,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué avec le livre. Elle a pris un yaourt. Elle a vu le chat. Le ronron du chat s'est tu, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9163,7 +9613,15 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué avec le livre.
+narrateur|Elle a pris un yaourt.
+narrateur|Elle a vu le chat.
+narrateur|Le ronron du chat s'est tu, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr"/>
@@ -9191,7 +9649,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint le chien. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de le livre, un yaourt et le chien. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>Le chien écoute, près de la page. Une goutte de yaourt brille, tout petit. Nina rejoint le chien. La cour sent l'herbe et la terre. J'ai écouté la maîtresse. J'ai eu un malaise. Je raconte à la maison. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à papa ou maman. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement. Elle se souvient du livre, et d'un yaourt.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9331,7 +9789,22 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Inès rejoint le chien. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de le livre, un yaourt et le chien. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>narrateur|Le chien écoute, près de la page.
+narrateur|Une goutte de yaourt brille, tout petit.
+narrateur|Nina rejoint le chien.
+narrateur|La cour sent l'herbe et la terre.
+enfant-f|J'ai écouté la maîtresse.
+enfant-f|J'ai eu un malaise.
+enfant-f|Je raconte à la maison.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à papa ou maman.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+narrateur|Elle se souvient du livre, et d'un yaourt.</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
@@ -9363,7 +9836,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué avec le livre. Elle a pris un yaourt. Elle a vu le chien. Le chien a posé la tête, puis dormi. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9503,7 +9976,15 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué avec le livre.
+narrateur|Elle a pris un yaourt.
+narrateur|Elle a vu le chien.
+narrateur|Le chien a posé la tête, puis dormi.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr"/>
@@ -9531,7 +10012,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint la poule. La lumière est claire. On se tait une seconde. Cette fin-là est celle de le livre, un yaourt et la poule. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>La poule picote le sol, loin du livre. Le yaourt attend sur le rebord. Nina rejoint la poule. La cour sent l'herbe et la terre. J'ai écouté la maîtresse. J'ai eu un malaise. Je raconte à la maison. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à papa ou maman. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement. Elle se souvient du livre, et d'un yaourt.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9671,7 +10152,22 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Inès rejoint la poule. La lumière est claire. On se tait une seconde. Cette fin-là est celle de le livre, un yaourt et la poule. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>narrateur|La poule picote le sol, loin du livre.
+narrateur|Le yaourt attend sur le rebord.
+narrateur|Nina rejoint la poule.
+narrateur|La cour sent l'herbe et la terre.
+enfant-f|J'ai écouté la maîtresse.
+enfant-f|J'ai eu un malaise.
+enfant-f|Je raconte à la maison.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à papa ou maman.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+narrateur|Elle se souvient du livre, et d'un yaourt.</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr"/>
@@ -9699,7 +10195,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué avec le livre. Elle a pris un yaourt. Elle a vu la poule. Une goutte de yaourt a séché sur le rebord. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9839,7 +10335,15 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué avec le livre.
+narrateur|Elle a pris un yaourt.
+narrateur|Elle a vu la poule.
+narrateur|Une goutte de yaourt a séché sur le rebord.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr"/>
@@ -9867,7 +10371,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Inès a choisi un morceau de pain. L'eau coule, tout petit bruit. Un morceau de pain reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès répète tout bas : écouter, si malaise raconter à la maison. On range un objet. maman n'est pas loin.</t>
+          <t>Nina a choisi un morceau de pain, près du livre. La croûte est un peu chaude. Des miettes tombent sur la table. On écoute, même avec le pain ? J'écoute la maîtresse. Si malaise, tu racontes. À la maison. À papa ou à maman. Bravo. C'est ça. Nina souffle une miette, tout léger. Tu as écouté. Tu as raconté. Mon ventre est calme. Le pain reste à sa place.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -10007,7 +10511,19 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Inès a choisi un morceau de pain. L'eau coule, tout petit bruit. Un morceau de pain reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès répète tout bas : écouter, si malaise raconter à la maison. On range un objet. maman n'est pas loin.</t>
+          <t>narrateur|Nina a choisi un morceau de pain, près du livre.
+narrateur|La croûte est un peu chaude.
+narrateur|Des miettes tombent sur la table.
+papa|On écoute, même avec le pain ?
+enfant-f|J'écoute la maîtresse.
+maman|Si malaise, tu racontes.
+enfant-f|À la maison.
+papa|À papa ou à maman.
+maman|Bravo. C'est ça.
+narrateur|Nina souffle une miette, tout léger.
+papa|Tu as écouté. Tu as raconté.
+enfant-f|Mon ventre est calme.
+narrateur|Le pain reste à sa place.</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr"/>
@@ -10035,7 +10551,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le chat, le chien, ou la poule.</t>
+          <t>On va voir qui, dans la cour ? Le chat, le chien, ou la poule.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10199,7 +10715,8 @@
       <c r="AV53" s="2" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+          <t>narrateur|On va voir qui, dans la cour ?
+papa|Le chat, le chien, ou la poule.</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
@@ -10231,7 +10748,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint le chat. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de le livre, un morceau de pain et le chat. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>Le chat a une miette sur la moustache. Le livre garde une page ouverte. Nina rejoint le chat. La cour sent l'herbe et la terre. J'ai écouté la maîtresse. J'ai eu un malaise. Je raconte à la maison. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à papa ou maman. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement. Elle se souvient du livre, et d'un morceau de pain.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10371,7 +10888,22 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Inès rejoint le chat. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de le livre, un morceau de pain et le chat. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>narrateur|Le chat a une miette sur la moustache.
+narrateur|Le livre garde une page ouverte.
+narrateur|Nina rejoint le chat.
+narrateur|La cour sent l'herbe et la terre.
+enfant-f|J'ai écouté la maîtresse.
+enfant-f|J'ai eu un malaise.
+enfant-f|Je raconte à la maison.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à papa ou maman.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+narrateur|Elle se souvient du livre, et d'un morceau de pain.</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr"/>
@@ -10399,7 +10931,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué avec le livre. Elle a pris un morceau de pain. Elle a vu le chat. La moustache du chat n'a plus de miette. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10539,7 +11071,15 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué avec le livre.
+narrateur|Elle a pris un morceau de pain.
+narrateur|Elle a vu le chat.
+narrateur|La moustache du chat n'a plus de miette.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr"/>
@@ -10567,7 +11107,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint le chien. La lumière est claire. On rit un peu. Cette fin-là est celle de le livre, un morceau de pain et le chien. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>Le chien reste assis pendant l'histoire. Une miette de pain dort sur la page. Nina rejoint le chien. La cour sent l'herbe et la terre. J'ai écouté la maîtresse. J'ai eu un malaise. Je raconte à la maison. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à papa ou maman. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement. Elle se souvient du livre, et d'un morceau de pain.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10707,7 +11247,22 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Inès rejoint le chien. La lumière est claire. On rit un peu. Cette fin-là est celle de le livre, un morceau de pain et le chien. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>narrateur|Le chien reste assis pendant l'histoire.
+narrateur|Une miette de pain dort sur la page.
+narrateur|Nina rejoint le chien.
+narrateur|La cour sent l'herbe et la terre.
+enfant-f|J'ai écouté la maîtresse.
+enfant-f|J'ai eu un malaise.
+enfant-f|Je raconte à la maison.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à papa ou maman.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+narrateur|Elle se souvient du livre, et d'un morceau de pain.</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
@@ -10739,7 +11294,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué avec le livre. Elle a pris un morceau de pain. Elle a vu le chien. La page sent encore le pain chaud. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10879,7 +11434,15 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué avec le livre.
+narrateur|Elle a pris un morceau de pain.
+narrateur|Elle a vu le chien.
+narrateur|La page sent encore le pain chaud.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr"/>
@@ -10907,7 +11470,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint la poule. Il y a des miettes sur la table. On se tait une seconde. Cette fin-là est celle de le livre, un morceau de pain et la poule. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>La poule écoute le livre, tout calme. Le pain repose près de la reliure. Nina rejoint la poule. La cour sent l'herbe et la terre. J'ai écouté la maîtresse. J'ai eu un malaise. Je raconte à la maison. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à papa ou maman. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement. Elle se souvient du livre, et d'un morceau de pain.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -11047,7 +11610,22 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Inès rejoint la poule. Il y a des miettes sur la table. On se tait une seconde. Cette fin-là est celle de le livre, un morceau de pain et la poule. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>narrateur|La poule écoute le livre, tout calme.
+narrateur|Le pain repose près de la reliure.
+narrateur|Nina rejoint la poule.
+narrateur|La cour sent l'herbe et la terre.
+enfant-f|J'ai écouté la maîtresse.
+enfant-f|J'ai eu un malaise.
+enfant-f|Je raconte à la maison.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à papa ou maman.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+narrateur|Elle se souvient du livre, et d'un morceau de pain.</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr"/>
@@ -11075,7 +11653,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué avec le livre. Elle a pris un morceau de pain. Elle a vu la poule. La reliure est chaude, près du radiateur. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11215,7 +11793,15 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué avec le livre.
+narrateur|Elle a pris un morceau de pain.
+narrateur|Elle a vu la poule.
+narrateur|La reliure est chaude, près du radiateur.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr"/>
@@ -11243,7 +11829,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Inès va vers la dînette. On entend un oiseau. papa sourit. Ici, c'est la dînette. Ce n'est pas comme les autres endroits. Inès se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On rit un peu. Je suis là. On reste ensemble.</t>
+          <t>Nina pose une tasse de dînette. La tasse est froide, toute petite. Ça sent presque la soupe, pour de rire. Papa tient une cuillère en bois. On écoute, même à la dînette ? J'écoute la maîtresse. Et le malaise, on le dit ? Oui. À la maison. À papa ou à maman. La maîtresse parle encore. Nina écoute, la tasse dans les mains. Bravo. C'est du bon travail. Tu as raconté ton malaise. Merci, maman. La petite casserole reste au calme.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11383,8 +11969,21 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|Inès va vers la dînette. On entend un oiseau. papa sourit. Ici, c'est la dînette. Ce n'est pas comme les autres endroits. Inès se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On rit un peu.
-papa|Je suis là. On reste ensemble.</t>
+          <t>narrateur|Nina pose une tasse de dînette.
+narrateur|La tasse est froide, toute petite.
+narrateur|Ça sent presque la soupe, pour de rire.
+narrateur|Papa tient une cuillère en bois.
+maman|On écoute, même à la dînette ?
+enfant-f|J'écoute la maîtresse.
+papa|Et le malaise, on le dit ?
+enfant-f|Oui. À la maison.
+maman|À papa ou à maman.
+narrateur|La maîtresse parle encore.
+narrateur|Nina écoute, la tasse dans les mains.
+papa|Bravo. C'est du bon travail.
+maman|Tu as raconté ton malaise.
+enfant-f|Merci, maman.
+narrateur|La petite casserole reste au calme.</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr"/>
@@ -11412,7 +12011,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
+          <t>On écoute qui ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -11572,7 +12171,7 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
+          <t>narrateur|On écoute qui ?</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr"/>
@@ -11600,7 +12199,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès respire. Inès retient : écouter, si malaise raconter à la maison. On continue, avec papa.</t>
+          <t>Oui. La maîtresse. Et si malaise, on raconte à la maison. Nina hoche la tête. Bravo, Nina. Tu as fait du bon travail. Merci, maman.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11744,7 +12343,13 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès respire. Inès retient : écouter, si malaise raconter à la maison. On continue, avec papa.</t>
+          <t>narrateur|Oui.
+papa|La maîtresse.
+maman|Et si malaise, on raconte à la maison.
+narrateur|Nina hoche la tête.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+enfant-f|Merci, maman.</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr"/>
@@ -11772,7 +12377,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+          <t>On prend quel goûter ? Une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -11936,7 +12541,8 @@
       <c r="AV63" s="2" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+          <t>narrateur|On prend quel goûter ?
+maman|Une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr"/>
@@ -11964,7 +12570,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Inès a choisi une pomme. Un vélo passe au loin. Une pomme reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès répète tout bas : écouter, si malaise raconter à la maison. On se tait une seconde. maman n'est pas loin.</t>
+          <t>Nina a choisi une pomme, près de la dînette. La pomme est rouge, un peu froide. Un oiseau chante derrière la vitre. Tu as encore le malaise ? Un peu. Je raconte. On écoute la maîtresse. Puis on raconte à la maison. Bravo. Tu as dit les mots. J'écoute. Je raconte. La pomme brille dans sa main. Le ventre se desserre, tout doux. On reste ensemble. Une feuille colle encore à la vitre.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12104,7 +12710,19 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Inès a choisi une pomme. Un vélo passe au loin. Une pomme reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès répète tout bas : écouter, si malaise raconter à la maison. On se tait une seconde. maman n'est pas loin.</t>
+          <t>narrateur|Nina a choisi une pomme, près de la dînette.
+narrateur|La pomme est rouge, un peu froide.
+narrateur|Un oiseau chante derrière la vitre.
+papa|Tu as encore le malaise ?
+enfant-f|Un peu. Je raconte.
+maman|On écoute la maîtresse.
+maman|Puis on raconte à la maison.
+papa|Bravo. Tu as dit les mots.
+enfant-f|J'écoute. Je raconte.
+narrateur|La pomme brille dans sa main.
+maman|Le ventre se desserre, tout doux.
+papa|On reste ensemble.
+narrateur|Une feuille colle encore à la vitre.</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr"/>
@@ -12132,7 +12750,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le chat, le chien, ou la poule.</t>
+          <t>On va voir qui, dans la cour ? Le chat, le chien, ou la poule.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12296,7 +12914,8 @@
       <c r="AV65" s="2" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+          <t>narrateur|On va voir qui, dans la cour ?
+papa|Le chat, le chien, ou la poule.</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
@@ -12328,7 +12947,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint le chat. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de la dînette, une pomme et le chat. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>Le chat touche la tasse de dînette, du nez. La pomme sert de gâteau, pour de rire. Nina rejoint le chat. La cour sent l'herbe et la terre. J'ai écouté la maîtresse. J'ai eu un malaise. Je raconte à la maison. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à papa ou maman. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement. Elle se souvient de la dînette, et d'une pomme.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12468,7 +13087,22 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Inès rejoint le chat. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de la dînette, une pomme et le chat. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>narrateur|Le chat touche la tasse de dînette, du nez.
+narrateur|La pomme sert de gâteau, pour de rire.
+narrateur|Nina rejoint le chat.
+narrateur|La cour sent l'herbe et la terre.
+enfant-f|J'ai écouté la maîtresse.
+enfant-f|J'ai eu un malaise.
+enfant-f|Je raconte à la maison.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à papa ou maman.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+narrateur|Elle se souvient de la dînette, et d'une pomme.</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr"/>
@@ -12496,7 +13130,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué avec la dînette. Elle a pris une pomme. Elle a vu le chat. La petite tasse a un rond de pomme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12636,7 +13270,15 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué avec la dînette.
+narrateur|Elle a pris une pomme.
+narrateur|Elle a vu le chat.
+narrateur|La petite tasse a un rond de pomme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr"/>
@@ -12664,7 +13306,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint le chien. Un vélo passe au loin. On se tait une seconde. Cette fin-là est celle de la dînette, une pomme et le chien. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>Le chien attend une pomme de dînette. La petite casserole est tiède. Nina rejoint le chien. La cour sent l'herbe et la terre. J'ai écouté la maîtresse. J'ai eu un malaise. Je raconte à la maison. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à papa ou maman. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement. Elle se souvient de la dînette, et d'une pomme.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12804,7 +13446,22 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Inès rejoint le chien. Un vélo passe au loin. On se tait une seconde. Cette fin-là est celle de la dînette, une pomme et le chien. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>narrateur|Le chien attend une pomme de dînette.
+narrateur|La petite casserole est tiède.
+narrateur|Nina rejoint le chien.
+narrateur|La cour sent l'herbe et la terre.
+enfant-f|J'ai écouté la maîtresse.
+enfant-f|J'ai eu un malaise.
+enfant-f|Je raconte à la maison.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à papa ou maman.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+narrateur|Elle se souvient de la dînette, et d'une pomme.</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
@@ -12836,7 +13493,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué avec la dînette. Elle a pris une pomme. Elle a vu le chien. La casserole de dînette s'est tue. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12976,7 +13633,15 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué avec la dînette.
+narrateur|Elle a pris une pomme.
+narrateur|Elle a vu le chien.
+narrateur|La casserole de dînette s'est tue.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr"/>
@@ -13004,7 +13669,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint la poule. La lumière est claire. On se tient la main. Cette fin-là est celle de la dînette, une pomme et la poule. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>La poule passe près de la petite casserole. Nina pose la pomme dans une assiette. Nina rejoint la poule. La cour sent l'herbe et la terre. J'ai écouté la maîtresse. J'ai eu un malaise. Je raconte à la maison. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à papa ou maman. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement. Elle se souvient de la dînette, et d'une pomme.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13144,7 +13809,22 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Inès rejoint la poule. La lumière est claire. On se tient la main. Cette fin-là est celle de la dînette, une pomme et la poule. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>narrateur|La poule passe près de la petite casserole.
+narrateur|Nina pose la pomme dans une assiette.
+narrateur|Nina rejoint la poule.
+narrateur|La cour sent l'herbe et la terre.
+enfant-f|J'ai écouté la maîtresse.
+enfant-f|J'ai eu un malaise.
+enfant-f|Je raconte à la maison.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à papa ou maman.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+narrateur|Elle se souvient de la dînette, et d'une pomme.</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr"/>
@@ -13172,7 +13852,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué avec la dînette. Elle a pris une pomme. Elle a vu la poule. L'assiette de dînette brille, vide. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13312,7 +13992,15 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué avec la dînette.
+narrateur|Elle a pris une pomme.
+narrateur|Elle a vu la poule.
+narrateur|L'assiette de dînette brille, vide.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr"/>
@@ -13340,7 +14028,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Inès a choisi un yaourt. La lumière est claire. Un yaourt reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès répète tout bas : écouter, si malaise raconter à la maison. On se tient la main. maman n'est pas loin.</t>
+          <t>Nina a choisi un yaourt, près de la dînette. Le pot est frais, tout lisse. Ça sent le lait, tout doux. Tu écoutes encore ? J'écoute la maîtresse. Et le malaise ? Je raconte à papa ou maman. Oui. À la maison aussi. Bravo, Nina. La cuillère fait un petit clic. Tu as fait du bon travail. Merci. Le pot reste près de la dînette.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13480,7 +14168,19 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Inès a choisi un yaourt. La lumière est claire. Un yaourt reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès répète tout bas : écouter, si malaise raconter à la maison. On se tient la main. maman n'est pas loin.</t>
+          <t>narrateur|Nina a choisi un yaourt, près de la dînette.
+narrateur|Le pot est frais, tout lisse.
+narrateur|Ça sent le lait, tout doux.
+maman|Tu écoutes encore ?
+enfant-f|J'écoute la maîtresse.
+papa|Et le malaise ?
+enfant-f|Je raconte à papa ou maman.
+maman|Oui. À la maison aussi.
+papa|Bravo, Nina.
+narrateur|La cuillère fait un petit clic.
+maman|Tu as fait du bon travail.
+enfant-f|Merci.
+narrateur|Le pot reste près de la dînette.</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr"/>
@@ -13508,7 +14208,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le chat, le chien, ou la poule.</t>
+          <t>On va voir qui, dans la cour ? Le chat, le chien, ou la poule.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13672,7 +14372,8 @@
       <c r="AV73" s="2" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+          <t>narrateur|On va voir qui, dans la cour ?
+papa|Le chat, le chien, ou la poule.</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
@@ -13704,7 +14405,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint le chat. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de la dînette, un yaourt et le chat. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>Le chat se couche près de la dînette. Le yaourt fait un goûter de poupée. Nina rejoint le chat. La cour sent l'herbe et la terre. J'ai écouté la maîtresse. J'ai eu un malaise. Je raconte à la maison. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à papa ou maman. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement. Elle se souvient de la dînette, et d'un yaourt.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13844,7 +14545,22 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Inès rejoint le chat. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de la dînette, un yaourt et le chat. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>narrateur|Le chat se couche près de la dînette.
+narrateur|Le yaourt fait un goûter de poupée.
+narrateur|Nina rejoint le chat.
+narrateur|La cour sent l'herbe et la terre.
+enfant-f|J'ai écouté la maîtresse.
+enfant-f|J'ai eu un malaise.
+enfant-f|Je raconte à la maison.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à papa ou maman.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+narrateur|Elle se souvient de la dînette, et d'un yaourt.</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr"/>
@@ -13872,7 +14588,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué avec la dînette. Elle a pris un yaourt. Elle a vu le chat. Le chat a laissé un creux près des tasses. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -14012,7 +14728,15 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué avec la dînette.
+narrateur|Elle a pris un yaourt.
+narrateur|Elle a vu le chat.
+narrateur|Le chat a laissé un creux près des tasses.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr"/>
@@ -14040,7 +14764,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint le chien. La lumière est claire. On se tait une seconde. Cette fin-là est celle de la dînette, un yaourt et le chien. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>Le chien ne prend pas la petite cuillère. Le pot de yaourt reste à sa place. Nina rejoint le chien. La cour sent l'herbe et la terre. J'ai écouté la maîtresse. J'ai eu un malaise. Je raconte à la maison. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à papa ou maman. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement. Elle se souvient de la dînette, et d'un yaourt.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14180,7 +14904,22 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Inès rejoint le chien. La lumière est claire. On se tait une seconde. Cette fin-là est celle de la dînette, un yaourt et le chien. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>narrateur|Le chien ne prend pas la petite cuillère.
+narrateur|Le pot de yaourt reste à sa place.
+narrateur|Nina rejoint le chien.
+narrateur|La cour sent l'herbe et la terre.
+enfant-f|J'ai écouté la maîtresse.
+enfant-f|J'ai eu un malaise.
+enfant-f|Je raconte à la maison.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à papa ou maman.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+narrateur|Elle se souvient de la dînette, et d'un yaourt.</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
@@ -14212,7 +14951,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué avec la dînette. Elle a pris un yaourt. Elle a vu le chien. La petite cuillère est rentrée dans la boîte. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14352,7 +15091,15 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué avec la dînette.
+narrateur|Elle a pris un yaourt.
+narrateur|Elle a vu le chien.
+narrateur|La petite cuillère est rentrée dans la boîte.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr"/>
@@ -14380,7 +15127,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint la poule. Il y a des miettes sur la table. On se tient la main. Cette fin-là est celle de la dînette, un yaourt et la poule. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>La poule fait cot cot, près des assiettes. Le yaourt brille comme de la crème. Nina rejoint la poule. La cour sent l'herbe et la terre. J'ai écouté la maîtresse. J'ai eu un malaise. Je raconte à la maison. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à papa ou maman. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement. Elle se souvient de la dînette, et d'un yaourt.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14520,7 +15267,22 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Inès rejoint la poule. Il y a des miettes sur la table. On se tient la main. Cette fin-là est celle de la dînette, un yaourt et la poule. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>narrateur|La poule fait cot cot, près des assiettes.
+narrateur|Le yaourt brille comme de la crème.
+narrateur|Nina rejoint la poule.
+narrateur|La cour sent l'herbe et la terre.
+enfant-f|J'ai écouté la maîtresse.
+enfant-f|J'ai eu un malaise.
+enfant-f|Je raconte à la maison.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à papa ou maman.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+narrateur|Elle se souvient de la dînette, et d'un yaourt.</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr"/>
@@ -14548,7 +15310,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué avec la dînette. Elle a pris un yaourt. Elle a vu la poule. Les assiettes de dînette sont en pile. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14688,7 +15450,15 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué avec la dînette.
+narrateur|Elle a pris un yaourt.
+narrateur|Elle a vu la poule.
+narrateur|Les assiettes de dînette sont en pile.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr"/>
@@ -14716,7 +15486,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Inès a choisi un morceau de pain. Il y a des miettes sur la table. Un morceau de pain reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès répète tout bas : écouter, si malaise raconter à la maison. On range un objet. maman n'est pas loin.</t>
+          <t>Nina a choisi un morceau de pain, près de la dînette. La croûte est un peu chaude. Des miettes tombent sur la table. On écoute, même avec le pain ? J'écoute la maîtresse. Si malaise, tu racontes. À la maison. À papa ou à maman. Bravo. C'est ça. Nina souffle une miette, tout léger. Tu as écouté. Tu as raconté. Mon ventre est calme. Le pain reste à sa place.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14856,7 +15626,19 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Inès a choisi un morceau de pain. Il y a des miettes sur la table. Un morceau de pain reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès répète tout bas : écouter, si malaise raconter à la maison. On range un objet. maman n'est pas loin.</t>
+          <t>narrateur|Nina a choisi un morceau de pain, près de la dînette.
+narrateur|La croûte est un peu chaude.
+narrateur|Des miettes tombent sur la table.
+papa|On écoute, même avec le pain ?
+enfant-f|J'écoute la maîtresse.
+maman|Si malaise, tu racontes.
+enfant-f|À la maison.
+papa|À papa ou à maman.
+maman|Bravo. C'est ça.
+narrateur|Nina souffle une miette, tout léger.
+papa|Tu as écouté. Tu as raconté.
+enfant-f|Mon ventre est calme.
+narrateur|Le pain reste à sa place.</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr"/>
@@ -14884,7 +15666,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le chat, le chien, ou la poule.</t>
+          <t>On va voir qui, dans la cour ? Le chat, le chien, ou la poule.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -15048,7 +15830,8 @@
       <c r="AV81" s="2" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+          <t>narrateur|On va voir qui, dans la cour ?
+papa|Le chat, le chien, ou la poule.</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
@@ -15080,7 +15863,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint le chat. La lumière est claire. On rit un peu. Cette fin-là est celle de la dînette, un morceau de pain et le chat. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>Le chat suit une miette vers la dînette. Le pain devient un gâteau, tout petit. Nina rejoint le chat. La cour sent l'herbe et la terre. J'ai écouté la maîtresse. J'ai eu un malaise. Je raconte à la maison. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à papa ou maman. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement. Elle se souvient de la dînette, et d'un morceau de pain.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15220,7 +16003,22 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Inès rejoint le chat. La lumière est claire. On rit un peu. Cette fin-là est celle de la dînette, un morceau de pain et le chat. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>narrateur|Le chat suit une miette vers la dînette.
+narrateur|Le pain devient un gâteau, tout petit.
+narrateur|Nina rejoint le chat.
+narrateur|La cour sent l'herbe et la terre.
+enfant-f|J'ai écouté la maîtresse.
+enfant-f|J'ai eu un malaise.
+enfant-f|Je raconte à la maison.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à papa ou maman.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+narrateur|Elle se souvient de la dînette, et d'un morceau de pain.</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr"/>
@@ -15248,7 +16046,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué avec la dînette. Elle a pris un morceau de pain. Elle a vu le chat. Une miette reste dans la petite casserole. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15388,7 +16186,15 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué avec la dînette.
+narrateur|Elle a pris un morceau de pain.
+narrateur|Elle a vu le chat.
+narrateur|Une miette reste dans la petite casserole.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr"/>
@@ -15416,7 +16222,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint le chien. Il y a des miettes sur la table. On se tait une seconde. Cette fin-là est celle de la dînette, un morceau de pain et le chien. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>Le chien reste près du pain, tout sage. La dînette a des miettes sur le bois. Nina rejoint le chien. La cour sent l'herbe et la terre. J'ai écouté la maîtresse. J'ai eu un malaise. Je raconte à la maison. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à papa ou maman. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement. Elle se souvient de la dînette, et d'un morceau de pain.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15556,7 +16362,22 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Inès rejoint le chien. Il y a des miettes sur la table. On se tait une seconde. Cette fin-là est celle de la dînette, un morceau de pain et le chien. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>narrateur|Le chien reste près du pain, tout sage.
+narrateur|La dînette a des miettes sur le bois.
+narrateur|Nina rejoint le chien.
+narrateur|La cour sent l'herbe et la terre.
+enfant-f|J'ai écouté la maîtresse.
+enfant-f|J'ai eu un malaise.
+enfant-f|Je raconte à la maison.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à papa ou maman.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+narrateur|Elle se souvient de la dînette, et d'un morceau de pain.</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
@@ -15588,7 +16409,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué avec la dînette. Elle a pris un morceau de pain. Elle a vu le chien. Le pain a une marque de dînette, tout drôle. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15728,7 +16549,15 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué avec la dînette.
+narrateur|Elle a pris un morceau de pain.
+narrateur|Elle a vu le chien.
+narrateur|Le pain a une marque de dînette, tout drôle.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr"/>
@@ -15756,7 +16585,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint la poule. Un chat miaule une fois. On se tient la main. Cette fin-là est celle de la dînette, un morceau de pain et la poule. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>La poule picore loin de la dînette. Nina range le pain dans une assiette. Nina rejoint la poule. La cour sent l'herbe et la terre. J'ai écouté la maîtresse. J'ai eu un malaise. Je raconte à la maison. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à papa ou maman. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement. Elle se souvient de la dînette, et d'un morceau de pain.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15896,7 +16725,22 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Inès rejoint la poule. Un chat miaule une fois. On se tient la main. Cette fin-là est celle de la dînette, un morceau de pain et la poule. Inès a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Inès a entendu : écouter, si malaise raconter à la maison. Inès dit merci à papa. On rentre.</t>
+          <t>narrateur|La poule picore loin de la dînette.
+narrateur|Nina range le pain dans une assiette.
+narrateur|Nina rejoint la poule.
+narrateur|La cour sent l'herbe et la terre.
+enfant-f|J'ai écouté la maîtresse.
+enfant-f|J'ai eu un malaise.
+enfant-f|Je raconte à la maison.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à papa ou maman.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+narrateur|Elle se souvient de la dînette, et d'un morceau de pain.</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr"/>
@@ -15924,7 +16768,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué avec la dînette. Elle a pris un morceau de pain. Elle a vu la poule. La dînette rentre dans le carton, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -16064,7 +16908,15 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué avec la dînette.
+narrateur|Elle a pris un morceau de pain.
+narrateur|Elle a vu la poule.
+narrateur|La dînette rentre dans le carton, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr"/>
@@ -16086,7 +16938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16124,6 +16976,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-COL-009.xlsx
+++ b/stories/arbres/TREE-COL-009.xlsx
@@ -5239,17 +5239,17 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Nina range le bouton dans le cartable. Une plume et une perle de yaourt voyagent ensemble. Ils se touchent, dans la poche. On le coud à la maison ? Oui, le fil est long. Le cube bosselé rentre aussi ? Oui, près du rouge. Le cartable se ferme sur la virgule de fil.</t>
+          <t>Nina range le bouton dans le cartable. Une plume et une perle de yaourt voyagent ensemble. Ils se touchent, dans la poche. On le coud à la maison ? Oui, le fil est long. Le cube bosselé rentre aussi ? Oui, près du rouge. Le cartable garde la plume et la perle, au chaud.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Nina range le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; dans le cartable. Une plume et une perle de yaourt voyagent ensemble. Ils se touchent, dans la poche. On le coud à la maison ? Oui, le fil est long. Le cube bosselé rentre aussi ? Oui, près du rouge. Le cartable se ferme sur la virgule de fil.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Nina range le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; dans le cartable. Une plume et une perle de yaourt voyagent ensemble. Ils se touchent, dans la poche. On le coud à la maison ? Oui, le fil est long. Le cube bosselé rentre aussi ? Oui, près du rouge. Le cartable garde la plume et la perle, au chaud.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Nina range le &lt;emphasis&gt;bouton&lt;/emphasis&gt; dans le cartable. Une plume et une perle de yaourt voyagent ensemble. Ils se touchent, dans la poche. On le coud à la maison ? Oui, le fil est long. Le cube bosselé rentre aussi ? Oui, près du rouge. Le cartable se ferme sur la virgule de fil.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Nina range le &lt;emphasis&gt;bouton&lt;/emphasis&gt; dans le cartable. Une plume et une perle de yaourt voyagent ensemble. Ils se touchent, dans la poche. On le coud à la maison ? Oui, le fil est long. Le cube bosselé rentre aussi ? Oui, près du rouge. Le cartable garde la plume et la perle, au chaud.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr"/>
@@ -5394,7 +5394,7 @@
 enfant-f|Oui, le fil est long.
 maman|Le cube bosselé rentre aussi ?
 enfant-f|Oui, près du rouge.
-narrateur|Le cartable se ferme sur la virgule de fil.</t>
+narrateur|Le cartable garde la plume et la perle, au chaud.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
@@ -15942,17 +15942,17 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Nina range bouton et tasse dans le cartable. Une plume colle à la perle de yaourt. La cerise voyage. On coud ce soir ? Oui, le fil est long. La dînette rentre aussi ? La tasse, oui. Le cartable se ferme sur la virgule de fil.</t>
+          <t>Nina range bouton et tasse dans le cartable. Une plume colle à la perle de yaourt. La cerise voyage. On coud ce soir ? Oui, le fil est long. La dînette rentre aussi ? La tasse, oui. La tasse cliquette une fois, puis plus rien.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Nina range &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; et tasse dans le cartable. Une plume colle à la perle de yaourt. La cerise voyage. On coud ce soir ? Oui, le fil est long. La dînette rentre aussi ? La tasse, oui. Le cartable se ferme sur la virgule de fil.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Nina range &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; et tasse dans le cartable. Une plume colle à la perle de yaourt. La cerise voyage. On coud ce soir ? Oui, le fil est long. La dînette rentre aussi ? La tasse, oui. La tasse cliquette une fois, puis plus rien.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Nina range &lt;emphasis&gt;bouton&lt;/emphasis&gt; et tasse dans le cartable. Une plume colle à la perle de yaourt. La cerise voyage. On coud ce soir ? Oui, le fil est long. La dînette rentre aussi ? La tasse, oui. Le cartable se ferme sur la virgule de fil.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Nina range &lt;emphasis&gt;bouton&lt;/emphasis&gt; et tasse dans le cartable. Une plume colle à la perle de yaourt. La cerise voyage. On coud ce soir ? Oui, le fil est long. La dînette rentre aussi ? La tasse, oui. La tasse cliquette une fois, puis plus rien.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr"/>
@@ -16097,7 +16097,7 @@
 enfant-f|Oui, le fil est long.
 maman|La dînette rentre aussi ?
 enfant-f|La tasse, oui.
-narrateur|Le cartable se ferme sur la virgule de fil.</t>
+narrateur|La tasse cliquette une fois, puis plus rien.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
@@ -16714,17 +16714,17 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Nina recoud au coin du crochet, la casserole à côté. Une miette et un poil de chat partagent le fil. Le trou est juste ? Juste. La dînette sent le pain, un peu. Le tic du radiateur suit le dernier point. Le manteau ferme, le crochet reste vide.</t>
+          <t>Nina recoud au coin du crochet, la casserole à côté. Une miette et un poil de chat partagent le fil. Le trou est juste ? Juste. La dînette sent le pain, un peu. Le tic du radiateur suit le dernier point. La casserole de dînette reste tiède, vide.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Nina recoud au coin du crochet, la casserole à côté. Une miette et un poil de chat partagent le fil. Le trou est juste ? Juste. La dînette sent le pain, un peu. Le tic du radiateur suit le dernier point. Le manteau ferme, le crochet reste vide.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Nina recoud au coin du crochet, la casserole à côté. Une miette et un poil de chat partagent le fil. Le trou est juste ? Juste. La dînette sent le pain, un peu. Le tic du radiateur suit le dernier point. La casserole de dînette reste tiède, vide.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Nina recoud au coin du crochet, la casserole à côté. Une miette et un poil de chat partagent le fil. Le trou est juste ? Juste. La dînette sent le pain, un peu. Le tic du radiateur suit le dernier point. Le manteau ferme, le crochet reste vide.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Nina recoud au coin du crochet, la casserole à côté. Une miette et un poil de chat partagent le fil. Le trou est juste ? Juste. La dînette sent le pain, un peu. Le tic du radiateur suit le dernier point. La casserole de dînette reste tiède, vide.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr"/>
@@ -16868,7 +16868,7 @@
 enfant-f|Juste.
 maman|La dînette sent le pain, un peu.
 narrateur|Le tic du radiateur suit le dernier point.
-narrateur|Le manteau ferme, le crochet reste vide.</t>
+narrateur|La casserole de dînette reste tiède, vide.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
@@ -17469,17 +17469,17 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Nina glisse le bouton dans le manteau, dehors. Une plume et une miette tiennent au fil. Ça raconte la poule, et le gâteau. La dînette rentre ? Oui, la soupe pour de rire est finie. Le trou est plein, maintenant ? Plein. La virgule de fil dépasse, comme un secret.</t>
+          <t>Nina glisse le bouton dans le manteau, dehors. Une plume et une miette tiennent au fil. Ça raconte la poule, et le gâteau. La dînette rentre ? Oui, la soupe pour de rire est finie. Le trou est plein, maintenant ? Plein. Une plume pique le col, tout léger.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Nina glisse le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; dans le manteau, dehors. Une plume et une miette tiennent au fil. Ça raconte la poule, et le gâteau. La dînette rentre ? Oui, la soupe pour de rire est finie. Le trou est plein, maintenant ? Plein. La virgule de fil dépasse, comme un secret.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Nina glisse le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; dans le manteau, dehors. Une plume et une miette tiennent au fil. Ça raconte la poule, et le gâteau. La dînette rentre ? Oui, la soupe pour de rire est finie. Le trou est plein, maintenant ? Plein. Une plume pique le col, tout léger.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Nina glisse le &lt;emphasis&gt;bouton&lt;/emphasis&gt; dans le manteau, dehors. Une plume et une miette tiennent au fil. Ça raconte la poule, et le gâteau. La dînette rentre ? Oui, la soupe pour de rire est finie. Le trou est plein, maintenant ? Plein. La virgule de fil dépasse, comme un secret.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Nina glisse le &lt;emphasis&gt;bouton&lt;/emphasis&gt; dans le manteau, dehors. Une plume et une miette tiennent au fil. Ça raconte la poule, et le gâteau. La dînette rentre ? Oui, la soupe pour de rire est finie. Le trou est plein, maintenant ? Plein. Une plume pique le col, tout léger.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr"/>
@@ -17624,7 +17624,7 @@
 enfant-f|Oui, la soupe pour de rire est finie.
 maman|Le trou est plein, maintenant ?
 enfant-f|Plein.
-narrateur|La virgule de fil dépasse, comme un secret.</t>
+narrateur|Une plume pique le col, tout léger.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
@@ -17650,7 +17650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -17707,6 +17707,13 @@
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
